--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,394 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132520634</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koludden, Koludden, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>568115</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6505513</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132520970</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96688</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koludden, Koludden, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568125</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6505568</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132522599</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96688</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Straffudden, Straffudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568157</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6505734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132522230</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Straffudden, Straffudden, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568157</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6505734</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,6 +1436,443 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132578519</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568126</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6505600</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132576302</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97765</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568178</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6505700</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132578536</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568116</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6505572</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132576650</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568181</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6505677</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96688</v>
+        <v>96696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96688</v>
+        <v>96696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79403</v>
+        <v>79405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97765</v>
+        <v>97773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96696</v>
+        <v>96706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96696</v>
+        <v>96706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97773</v>
+        <v>97783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96706</v>
+        <v>96707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96706</v>
+        <v>96707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97783</v>
+        <v>97784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96707</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97784</v>
+        <v>97785</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>91931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132520970</v>
+        <v>132522599</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>96709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568125</v>
+        <v>568157</v>
       </c>
       <c r="R6" t="n">
-        <v>6505568</v>
+        <v>6505734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132522599</v>
+        <v>132520970</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>96709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568157</v>
+        <v>568125</v>
       </c>
       <c r="R7" t="n">
-        <v>6505734</v>
+        <v>6505568</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97785</v>
+        <v>97786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132522599</v>
+        <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568157</v>
+        <v>568125</v>
       </c>
       <c r="R6" t="n">
-        <v>6505734</v>
+        <v>6505568</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132520970</v>
+        <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568125</v>
+        <v>568157</v>
       </c>
       <c r="R7" t="n">
-        <v>6505568</v>
+        <v>6505734</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97786</v>
+        <v>97788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96711</v>
+        <v>96712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96711</v>
+        <v>96712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97788</v>
+        <v>97789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132520970</v>
+        <v>132522599</v>
       </c>
       <c r="B6" t="n">
-        <v>96712</v>
+        <v>96715</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568125</v>
+        <v>568157</v>
       </c>
       <c r="R6" t="n">
-        <v>6505568</v>
+        <v>6505734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132522599</v>
+        <v>132520970</v>
       </c>
       <c r="B7" t="n">
-        <v>96712</v>
+        <v>96715</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568157</v>
+        <v>568125</v>
       </c>
       <c r="R7" t="n">
-        <v>6505734</v>
+        <v>6505568</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79415</v>
+        <v>79418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97789</v>
+        <v>97792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132522599</v>
+        <v>132520970</v>
       </c>
       <c r="B6" t="n">
         <v>96715</v>
@@ -1178,17 +1178,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568157</v>
+        <v>568125</v>
       </c>
       <c r="R6" t="n">
-        <v>6505734</v>
+        <v>6505568</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132520970</v>
+        <v>132522599</v>
       </c>
       <c r="B7" t="n">
         <v>96715</v>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568125</v>
+        <v>568157</v>
       </c>
       <c r="R7" t="n">
-        <v>6505568</v>
+        <v>6505734</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91937</v>
+        <v>91938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>132520970</v>
       </c>
       <c r="B6" t="n">
-        <v>96715</v>
+        <v>96716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132522599</v>
       </c>
       <c r="B7" t="n">
-        <v>96715</v>
+        <v>96716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97792</v>
+        <v>97793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>132520634</v>
       </c>
       <c r="B5" t="n">
-        <v>91938</v>
+        <v>91939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132520970</v>
+        <v>132522599</v>
       </c>
       <c r="B6" t="n">
-        <v>96716</v>
+        <v>96718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,17 +1178,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568125</v>
+        <v>568157</v>
       </c>
       <c r="R6" t="n">
-        <v>6505568</v>
+        <v>6505734</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132522599</v>
+        <v>132520970</v>
       </c>
       <c r="B7" t="n">
-        <v>96716</v>
+        <v>96718</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,17 +1275,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568157</v>
+        <v>568125</v>
       </c>
       <c r="R7" t="n">
-        <v>6505734</v>
+        <v>6505568</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>132522230</v>
       </c>
       <c r="B8" t="n">
-        <v>79418</v>
+        <v>79419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>132578519</v>
       </c>
       <c r="B9" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>132576302</v>
       </c>
       <c r="B10" t="n">
-        <v>97793</v>
+        <v>97797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>132578536</v>
       </c>
       <c r="B11" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>132576650</v>
       </c>
       <c r="B12" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96782101</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568175.5787065782</v>
+        <v>568176</v>
       </c>
       <c r="R2" t="n">
-        <v>6505727.778857049</v>
+        <v>6505728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2021-10-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,66 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112686016</v>
+        <v>132520970</v>
       </c>
       <c r="B3" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torshags skjutbana markörgraven NO 380 m, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568124</v>
+        <v>568125</v>
       </c>
       <c r="R3" t="n">
-        <v>6505594</v>
+        <v>6505568</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,93 +861,66 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112686067</v>
+        <v>132522599</v>
       </c>
       <c r="B4" t="n">
-        <v>97021</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torshags skjutbana markörgraven NO 390 m, Ög</t>
+          <t>Straffudden, Straffudden, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568129</v>
+        <v>568157</v>
       </c>
       <c r="R4" t="n">
-        <v>6505608</v>
+        <v>6505734</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,17 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 70 skott</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,69 +958,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132520634</v>
+        <v>132576302</v>
       </c>
       <c r="B5" t="n">
-        <v>91939</v>
+        <v>97862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Koludden, Koludden, Ög</t>
+          <t>Sydost Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568115</v>
+        <v>568178</v>
       </c>
       <c r="R5" t="n">
-        <v>6505513</v>
+        <v>6505700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,56 +1053,62 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132520970</v>
+        <v>132520634</v>
       </c>
       <c r="B6" t="n">
-        <v>96718</v>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568125</v>
+        <v>568115</v>
       </c>
       <c r="R6" t="n">
-        <v>6505568</v>
+        <v>6505513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132522599</v>
+        <v>132522230</v>
       </c>
       <c r="B7" t="n">
-        <v>96718</v>
+        <v>79459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,7 +1221,7 @@
         <v>6505734</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132522230</v>
+        <v>132576803</v>
       </c>
       <c r="B8" t="n">
-        <v>79419</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,37 +1288,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Straffudden, Straffudden, Ög</t>
+          <t>Sydost Södra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568157</v>
+        <v>568115</v>
       </c>
       <c r="R8" t="n">
-        <v>6505734</v>
+        <v>6505789</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,6 +1356,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska spår i basen av fem döda granar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,72 +1375,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132578519</v>
+        <v>132520277</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>4782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öster om Södra Granstorp, Ög</t>
+          <t>Koludden, Koludden, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568126</v>
+        <v>568075</v>
       </c>
       <c r="R9" t="n">
-        <v>6505600</v>
+        <v>6505437</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,68 +1466,79 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132576302</v>
+        <v>112686016</v>
       </c>
       <c r="B10" t="n">
-        <v>97797</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydost Södra Granstorp, Ög</t>
+          <t>Torshags skjutbana markörgraven NO 380 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568178</v>
+        <v>568124</v>
       </c>
       <c r="R10" t="n">
-        <v>6505700</v>
+        <v>6505594</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,17 +1565,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På asp</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,25 +1583,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132578536</v>
+        <v>112686067</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,27 +1633,31 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öster om Södra Granstorp, Ög</t>
+          <t>Torshags skjutbana markörgraven NO 390 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568116</v>
+        <v>568129</v>
       </c>
       <c r="R11" t="n">
-        <v>6505572</v>
+        <v>6505608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,12 +1684,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-10-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 70 skott</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,25 +1707,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132576650</v>
+        <v>113686884</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,27 +1757,31 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sydost Södra Granstorp, Ög</t>
+          <t>Torshags skjutbana markörgraven NO 225 m, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568181</v>
+        <v>568056</v>
       </c>
       <c r="R12" t="n">
-        <v>6505677</v>
+        <v>6505452</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,12 +1808,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,18 +1826,472 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132576650</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sydost Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568181</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6505677</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132578519</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568126</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6505600</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132578536</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster om Södra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568116</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6505572</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121440898</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torshags skjutbana markörgraven NO 225 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>568056</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6505452</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17463-2026 artfynd.xlsx
+++ b/artfynd/A 17463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96782101</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132522599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132576302</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520634</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132522230</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132576803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520277</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112686016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112686067</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113686884</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132576650</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132578519</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2173,6 +2243,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132578536</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,8 +2367,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121440898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>